--- a/exports/eth-usd_predictions_last90.xlsx
+++ b/exports/eth-usd_predictions_last90.xlsx
@@ -453,1441 +453,1441 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4426.18</v>
+        <v>4312.5</v>
       </c>
       <c r="C2" t="n">
-        <v>4458.06</v>
+        <v>4355.2</v>
       </c>
       <c r="D2" t="n">
-        <v>31.88</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4473.27</v>
+        <v>4073.46</v>
       </c>
       <c r="C3" t="n">
-        <v>4461.76</v>
+        <v>4185.37</v>
       </c>
       <c r="D3" t="n">
-        <v>-11.51</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4312.5</v>
+        <v>4334.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4355.23</v>
+        <v>4225.35</v>
       </c>
       <c r="D4" t="n">
-        <v>42.73</v>
+        <v>-109.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4073.46</v>
+        <v>4223.21</v>
       </c>
       <c r="C5" t="n">
-        <v>4185.38</v>
+        <v>4298.92</v>
       </c>
       <c r="D5" t="n">
-        <v>111.92</v>
+        <v>75.70999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4334.5</v>
+        <v>4831.35</v>
       </c>
       <c r="C6" t="n">
-        <v>4225.51</v>
+        <v>4475.35</v>
       </c>
       <c r="D6" t="n">
-        <v>-108.99</v>
+        <v>-356</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4223.21</v>
+        <v>4776.09</v>
       </c>
       <c r="C7" t="n">
-        <v>4299.08</v>
+        <v>4753.24</v>
       </c>
       <c r="D7" t="n">
-        <v>75.87</v>
+        <v>-22.85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4831.35</v>
+        <v>4779.65</v>
       </c>
       <c r="C8" t="n">
-        <v>4475.36</v>
+        <v>4809.5</v>
       </c>
       <c r="D8" t="n">
-        <v>-355.99</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4776.09</v>
+        <v>4372.99</v>
       </c>
       <c r="C9" t="n">
-        <v>4753.35</v>
+        <v>4604.56</v>
       </c>
       <c r="D9" t="n">
-        <v>-22.74</v>
+        <v>231.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4779.65</v>
+        <v>4600.43</v>
       </c>
       <c r="C10" t="n">
-        <v>4809.33</v>
+        <v>4509.73</v>
       </c>
       <c r="D10" t="n">
-        <v>29.68</v>
+        <v>-90.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4372.99</v>
+        <v>4503.39</v>
       </c>
       <c r="C11" t="n">
-        <v>4604.64</v>
+        <v>4539.53</v>
       </c>
       <c r="D11" t="n">
-        <v>231.65</v>
+        <v>36.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4600.43</v>
+        <v>4507.18</v>
       </c>
       <c r="C12" t="n">
-        <v>4509.8</v>
+        <v>4478.02</v>
       </c>
       <c r="D12" t="n">
-        <v>-90.63</v>
+        <v>-29.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4503.39</v>
+        <v>4360.15</v>
       </c>
       <c r="C13" t="n">
-        <v>4539.77</v>
+        <v>4412.82</v>
       </c>
       <c r="D13" t="n">
-        <v>36.38</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4507.18</v>
+        <v>4374.15</v>
       </c>
       <c r="C14" t="n">
-        <v>4477.98</v>
+        <v>4412.31</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.2</v>
+        <v>38.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4360.15</v>
+        <v>4390.02</v>
       </c>
       <c r="C15" t="n">
-        <v>4412.93</v>
+        <v>4424.27</v>
       </c>
       <c r="D15" t="n">
-        <v>52.77</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4374.15</v>
+        <v>4314.47</v>
       </c>
       <c r="C16" t="n">
-        <v>4412.39</v>
+        <v>4358.77</v>
       </c>
       <c r="D16" t="n">
-        <v>38.24</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4390.02</v>
+        <v>4325.37</v>
       </c>
       <c r="C17" t="n">
-        <v>4424.42</v>
+        <v>4335.41</v>
       </c>
       <c r="D17" t="n">
-        <v>34.4</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4314.47</v>
+        <v>4450.39</v>
       </c>
       <c r="C18" t="n">
-        <v>4358.81</v>
+        <v>4401.02</v>
       </c>
       <c r="D18" t="n">
-        <v>44.34</v>
+        <v>-49.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4325.37</v>
+        <v>4298.74</v>
       </c>
       <c r="C19" t="n">
-        <v>4335.44</v>
+        <v>4404.72</v>
       </c>
       <c r="D19" t="n">
-        <v>10.08</v>
+        <v>105.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4450.39</v>
+        <v>4306.99</v>
       </c>
       <c r="C20" t="n">
-        <v>4401.1</v>
+        <v>4314.91</v>
       </c>
       <c r="D20" t="n">
-        <v>-49.29</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4298.74</v>
+        <v>4274.24</v>
       </c>
       <c r="C21" t="n">
-        <v>4404.76</v>
+        <v>4302.71</v>
       </c>
       <c r="D21" t="n">
-        <v>106.02</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4306.99</v>
+        <v>4305.35</v>
       </c>
       <c r="C22" t="n">
-        <v>4314.9</v>
+        <v>4313.23</v>
       </c>
       <c r="D22" t="n">
-        <v>7.91</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4274.24</v>
+        <v>4308.07</v>
       </c>
       <c r="C23" t="n">
-        <v>4302.81</v>
+        <v>4289.74</v>
       </c>
       <c r="D23" t="n">
-        <v>28.57</v>
+        <v>-18.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4305.35</v>
+        <v>4309.04</v>
       </c>
       <c r="C24" t="n">
-        <v>4313.27</v>
+        <v>4295.61</v>
       </c>
       <c r="D24" t="n">
-        <v>7.92</v>
+        <v>-13.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4308.07</v>
+        <v>4349.15</v>
       </c>
       <c r="C25" t="n">
-        <v>4289.79</v>
+        <v>4328.24</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.28</v>
+        <v>-20.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4309.04</v>
+        <v>4461.23</v>
       </c>
       <c r="C26" t="n">
-        <v>4295.65</v>
+        <v>4392.79</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.39</v>
+        <v>-68.44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4349.15</v>
+        <v>4715.25</v>
       </c>
       <c r="C27" t="n">
-        <v>4328.3</v>
+        <v>4539.38</v>
       </c>
       <c r="D27" t="n">
-        <v>-20.84</v>
+        <v>-175.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4461.23</v>
+        <v>4668.18</v>
       </c>
       <c r="C28" t="n">
-        <v>4392.85</v>
+        <v>4653.53</v>
       </c>
       <c r="D28" t="n">
-        <v>-68.39</v>
+        <v>-14.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4715.25</v>
+        <v>4609.6</v>
       </c>
       <c r="C29" t="n">
-        <v>4539.44</v>
+        <v>4625.29</v>
       </c>
       <c r="D29" t="n">
-        <v>-175.81</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4668.18</v>
+        <v>4526.82</v>
       </c>
       <c r="C30" t="n">
-        <v>4653.55</v>
+        <v>4555.71</v>
       </c>
       <c r="D30" t="n">
-        <v>-14.63</v>
+        <v>28.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4609.6</v>
+        <v>4503.56</v>
       </c>
       <c r="C31" t="n">
-        <v>4625.25</v>
+        <v>4517.46</v>
       </c>
       <c r="D31" t="n">
-        <v>15.65</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4526.82</v>
+        <v>4592.73</v>
       </c>
       <c r="C32" t="n">
-        <v>4555.79</v>
+        <v>4509.18</v>
       </c>
       <c r="D32" t="n">
-        <v>28.97</v>
+        <v>-83.56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4503.56</v>
+        <v>4589.92</v>
       </c>
       <c r="C33" t="n">
-        <v>4517.55</v>
+        <v>4556.71</v>
       </c>
       <c r="D33" t="n">
-        <v>13.98</v>
+        <v>-33.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4592.73</v>
+        <v>4470.92</v>
       </c>
       <c r="C34" t="n">
-        <v>4509.28</v>
+        <v>4538.53</v>
       </c>
       <c r="D34" t="n">
-        <v>-83.45</v>
+        <v>67.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4589.92</v>
+        <v>4482.27</v>
       </c>
       <c r="C35" t="n">
-        <v>4556.78</v>
+        <v>4481.83</v>
       </c>
       <c r="D35" t="n">
-        <v>-33.14</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4470.92</v>
+        <v>4451.33</v>
       </c>
       <c r="C36" t="n">
-        <v>4538.53</v>
+        <v>4478.64</v>
       </c>
       <c r="D36" t="n">
-        <v>67.62</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4482.27</v>
+        <v>4202.88</v>
       </c>
       <c r="C37" t="n">
-        <v>4481.92</v>
+        <v>4311.03</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.35</v>
+        <v>108.15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4451.33</v>
+        <v>4165.5</v>
       </c>
       <c r="C38" t="n">
-        <v>4478.73</v>
+        <v>4163.58</v>
       </c>
       <c r="D38" t="n">
-        <v>27.4</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4202.88</v>
+        <v>4153.47</v>
       </c>
       <c r="C39" t="n">
-        <v>4311.07</v>
+        <v>4144.11</v>
       </c>
       <c r="D39" t="n">
-        <v>108.19</v>
+        <v>-9.359999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4165.5</v>
+        <v>3868.33</v>
       </c>
       <c r="C40" t="n">
-        <v>4163.66</v>
+        <v>4014.59</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.84</v>
+        <v>146.26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4153.47</v>
+        <v>4035.89</v>
       </c>
       <c r="C41" t="n">
-        <v>4144.29</v>
+        <v>3942.48</v>
       </c>
       <c r="D41" t="n">
-        <v>-9.18</v>
+        <v>-93.40000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3868.33</v>
+        <v>4018.66</v>
       </c>
       <c r="C42" t="n">
-        <v>4014.63</v>
+        <v>4023.39</v>
       </c>
       <c r="D42" t="n">
-        <v>146.29</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4035.89</v>
+        <v>4141.48</v>
       </c>
       <c r="C43" t="n">
-        <v>3942.56</v>
+        <v>4104.54</v>
       </c>
       <c r="D43" t="n">
-        <v>-93.31999999999999</v>
+        <v>-36.94</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4018.66</v>
+        <v>4217.34</v>
       </c>
       <c r="C44" t="n">
-        <v>4023.57</v>
+        <v>4146.62</v>
       </c>
       <c r="D44" t="n">
-        <v>4.91</v>
+        <v>-70.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4141.48</v>
+        <v>4145.96</v>
       </c>
       <c r="C45" t="n">
-        <v>4104.55</v>
+        <v>4195.06</v>
       </c>
       <c r="D45" t="n">
-        <v>-36.93</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4217.34</v>
+        <v>4351.11</v>
       </c>
       <c r="C46" t="n">
-        <v>4146.69</v>
+        <v>4251.11</v>
       </c>
       <c r="D46" t="n">
-        <v>-70.65000000000001</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4145.96</v>
+        <v>4487.92</v>
       </c>
       <c r="C47" t="n">
-        <v>4195.05</v>
+        <v>4376.22</v>
       </c>
       <c r="D47" t="n">
-        <v>49.1</v>
+        <v>-111.71</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4351.11</v>
+        <v>4514.87</v>
       </c>
       <c r="C48" t="n">
-        <v>4251.15</v>
+        <v>4475.56</v>
       </c>
       <c r="D48" t="n">
-        <v>-99.95999999999999</v>
+        <v>-39.31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4487.92</v>
+        <v>4489.2</v>
       </c>
       <c r="C49" t="n">
-        <v>4376.29</v>
+        <v>4462.58</v>
       </c>
       <c r="D49" t="n">
-        <v>-111.63</v>
+        <v>-26.62</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4514.87</v>
+        <v>4515.42</v>
       </c>
       <c r="C50" t="n">
-        <v>4475.51</v>
+        <v>4477.57</v>
       </c>
       <c r="D50" t="n">
-        <v>-39.36</v>
+        <v>-37.85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4489.2</v>
+        <v>4687.77</v>
       </c>
       <c r="C51" t="n">
-        <v>4462.57</v>
+        <v>4578.06</v>
       </c>
       <c r="D51" t="n">
-        <v>-26.62</v>
+        <v>-109.71</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4515.42</v>
+        <v>4451.15</v>
       </c>
       <c r="C52" t="n">
-        <v>4477.6</v>
+        <v>4550.15</v>
       </c>
       <c r="D52" t="n">
-        <v>-37.82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4687.77</v>
+        <v>4527.65</v>
       </c>
       <c r="C53" t="n">
-        <v>4578.13</v>
+        <v>4466.4</v>
       </c>
       <c r="D53" t="n">
-        <v>-109.64</v>
+        <v>-61.25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4451.15</v>
+        <v>4369.14</v>
       </c>
       <c r="C54" t="n">
-        <v>4550.16</v>
+        <v>4435.68</v>
       </c>
       <c r="D54" t="n">
-        <v>99.01000000000001</v>
+        <v>66.54000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4527.65</v>
+        <v>3843.01</v>
       </c>
       <c r="C55" t="n">
-        <v>4466.38</v>
+        <v>4119.02</v>
       </c>
       <c r="D55" t="n">
-        <v>-61.27</v>
+        <v>276.01</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4369.14</v>
+        <v>3750.61</v>
       </c>
       <c r="C56" t="n">
-        <v>4435.84</v>
+        <v>3767.49</v>
       </c>
       <c r="D56" t="n">
-        <v>66.69</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3843.01</v>
+        <v>4164.43</v>
       </c>
       <c r="C57" t="n">
-        <v>4119</v>
+        <v>3944.21</v>
       </c>
       <c r="D57" t="n">
-        <v>275.99</v>
+        <v>-220.22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3750.61</v>
+        <v>4245.47</v>
       </c>
       <c r="C58" t="n">
-        <v>3767.61</v>
+        <v>4196.78</v>
       </c>
       <c r="D58" t="n">
-        <v>17</v>
+        <v>-48.69</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4164.43</v>
+        <v>4125.41</v>
       </c>
       <c r="C59" t="n">
-        <v>3944.51</v>
+        <v>4145.49</v>
       </c>
       <c r="D59" t="n">
-        <v>-219.91</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4245.47</v>
+        <v>3987.46</v>
       </c>
       <c r="C60" t="n">
-        <v>4196.91</v>
+        <v>4068.08</v>
       </c>
       <c r="D60" t="n">
-        <v>-48.56</v>
+        <v>80.62</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4125.41</v>
+        <v>3894.75</v>
       </c>
       <c r="C61" t="n">
-        <v>4145.43</v>
+        <v>4031.33</v>
       </c>
       <c r="D61" t="n">
-        <v>20.02</v>
+        <v>136.57</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3987.46</v>
+        <v>3832.56</v>
       </c>
       <c r="C62" t="n">
-        <v>4068.14</v>
+        <v>3878.86</v>
       </c>
       <c r="D62" t="n">
-        <v>80.68000000000001</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3894.75</v>
+        <v>3890.35</v>
       </c>
       <c r="C63" t="n">
-        <v>4031.45</v>
+        <v>3812</v>
       </c>
       <c r="D63" t="n">
-        <v>136.7</v>
+        <v>-78.34</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3832.56</v>
+        <v>3984.65</v>
       </c>
       <c r="C64" t="n">
-        <v>3878.96</v>
+        <v>3892.91</v>
       </c>
       <c r="D64" t="n">
-        <v>46.4</v>
+        <v>-91.73999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3890.35</v>
+        <v>3980.76</v>
       </c>
       <c r="C65" t="n">
-        <v>3812.08</v>
+        <v>3973.02</v>
       </c>
       <c r="D65" t="n">
-        <v>-78.27</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3984.65</v>
+        <v>3876.76</v>
       </c>
       <c r="C66" t="n">
-        <v>3892.99</v>
+        <v>3927.01</v>
       </c>
       <c r="D66" t="n">
-        <v>-91.66</v>
+        <v>50.24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3980.76</v>
+        <v>3808.12</v>
       </c>
       <c r="C67" t="n">
-        <v>3973.06</v>
+        <v>3847.05</v>
       </c>
       <c r="D67" t="n">
-        <v>-7.7</v>
+        <v>38.93</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3876.76</v>
+        <v>3856.03</v>
       </c>
       <c r="C68" t="n">
-        <v>3927.03</v>
+        <v>3841.24</v>
       </c>
       <c r="D68" t="n">
-        <v>50.27</v>
+        <v>-14.79</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3808.12</v>
+        <v>3934.57</v>
       </c>
       <c r="C69" t="n">
-        <v>3847.11</v>
+        <v>3880.94</v>
       </c>
       <c r="D69" t="n">
-        <v>38.98</v>
+        <v>-53.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3856.03</v>
+        <v>3953.47</v>
       </c>
       <c r="C70" t="n">
-        <v>3841.32</v>
+        <v>3919.36</v>
       </c>
       <c r="D70" t="n">
-        <v>-14.71</v>
+        <v>-34.11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3934.57</v>
+        <v>4157.99</v>
       </c>
       <c r="C71" t="n">
-        <v>3881</v>
+        <v>4033.18</v>
       </c>
       <c r="D71" t="n">
-        <v>-53.56</v>
+        <v>-124.81</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3953.47</v>
+        <v>4120.12</v>
       </c>
       <c r="C72" t="n">
-        <v>3919.39</v>
+        <v>4132.89</v>
       </c>
       <c r="D72" t="n">
-        <v>-34.08</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4157.99</v>
+        <v>3982.26</v>
       </c>
       <c r="C73" t="n">
-        <v>4033.19</v>
+        <v>4064.81</v>
       </c>
       <c r="D73" t="n">
-        <v>-124.8</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4120.12</v>
+        <v>3903.35</v>
       </c>
       <c r="C74" t="n">
-        <v>4132.93</v>
+        <v>3931.48</v>
       </c>
       <c r="D74" t="n">
-        <v>12.81</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3982.26</v>
+        <v>3804.38</v>
       </c>
       <c r="C75" t="n">
-        <v>4064.76</v>
+        <v>3849.54</v>
       </c>
       <c r="D75" t="n">
-        <v>82.5</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3903.35</v>
+        <v>3847.08</v>
       </c>
       <c r="C76" t="n">
-        <v>3931.53</v>
+        <v>3817.01</v>
       </c>
       <c r="D76" t="n">
-        <v>28.17</v>
+        <v>-30.07</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3804.38</v>
+        <v>3874.19</v>
       </c>
       <c r="C77" t="n">
-        <v>3849.63</v>
+        <v>3823.93</v>
       </c>
       <c r="D77" t="n">
-        <v>45.25</v>
+        <v>-50.26</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3847.08</v>
+        <v>3911.06</v>
       </c>
       <c r="C78" t="n">
-        <v>3817.07</v>
+        <v>3871.74</v>
       </c>
       <c r="D78" t="n">
-        <v>-30.01</v>
+        <v>-39.33</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3874.19</v>
+        <v>3602.31</v>
       </c>
       <c r="C79" t="n">
-        <v>3824</v>
+        <v>3730.23</v>
       </c>
       <c r="D79" t="n">
-        <v>-50.18</v>
+        <v>127.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3911.06</v>
+        <v>3292.57</v>
       </c>
       <c r="C80" t="n">
-        <v>3871.78</v>
+        <v>3419.16</v>
       </c>
       <c r="D80" t="n">
-        <v>-39.28</v>
+        <v>126.59</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3602.31</v>
+        <v>3425.17</v>
       </c>
       <c r="C81" t="n">
-        <v>3730.25</v>
+        <v>3367.41</v>
       </c>
       <c r="D81" t="n">
-        <v>127.95</v>
+        <v>-57.77</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3292.57</v>
+        <v>3312.26</v>
       </c>
       <c r="C82" t="n">
-        <v>3419.17</v>
+        <v>3334.11</v>
       </c>
       <c r="D82" t="n">
-        <v>126.59</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3425.17</v>
+        <v>3435.3</v>
       </c>
       <c r="C83" t="n">
-        <v>3367.56</v>
+        <v>3348.9</v>
       </c>
       <c r="D83" t="n">
-        <v>-57.61</v>
+        <v>-86.40000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3312.26</v>
+        <v>3400.38</v>
       </c>
       <c r="C84" t="n">
-        <v>3334.25</v>
+        <v>3371.21</v>
       </c>
       <c r="D84" t="n">
-        <v>21.99</v>
+        <v>-29.17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3435.3</v>
+        <v>3582.62</v>
       </c>
       <c r="C85" t="n">
-        <v>3348.91</v>
+        <v>3540.05</v>
       </c>
       <c r="D85" t="n">
-        <v>-86.39</v>
+        <v>-42.57</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3400.38</v>
+        <v>3568.46</v>
       </c>
       <c r="C86" t="n">
-        <v>3371.3</v>
+        <v>3593.03</v>
       </c>
       <c r="D86" t="n">
-        <v>-29.07</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3582.62</v>
+        <v>3415.28</v>
       </c>
       <c r="C87" t="n">
-        <v>3540.1</v>
+        <v>3494.22</v>
       </c>
       <c r="D87" t="n">
-        <v>-42.52</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3568.46</v>
+        <v>3413.09</v>
       </c>
       <c r="C88" t="n">
-        <v>3593.09</v>
+        <v>3408.12</v>
       </c>
       <c r="D88" t="n">
-        <v>24.63</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3415.28</v>
+        <v>3232.76</v>
       </c>
       <c r="C89" t="n">
-        <v>3494.15</v>
+        <v>3296.41</v>
       </c>
       <c r="D89" t="n">
-        <v>78.87</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3413.09</v>
+        <v>3103.79</v>
       </c>
       <c r="C90" t="n">
-        <v>3408.14</v>
+        <v>3142.54</v>
       </c>
       <c r="D90" t="n">
-        <v>-4.95</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3232.76</v>
+        <v>3166.63</v>
       </c>
       <c r="C91" t="n">
-        <v>3296.46</v>
+        <v>3107.95</v>
       </c>
       <c r="D91" t="n">
-        <v>63.7</v>
+        <v>-58.68</v>
       </c>
     </row>
   </sheetData>

--- a/exports/eth-usd_predictions_last90.xlsx
+++ b/exports/eth-usd_predictions_last90.xlsx
@@ -453,1441 +453,1441 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4312.5</v>
+        <v>4831.35</v>
       </c>
       <c r="C2" t="n">
-        <v>4355.2</v>
+        <v>4475.58</v>
       </c>
       <c r="D2" t="n">
-        <v>42.69</v>
+        <v>-355.77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4073.46</v>
+        <v>4776.09</v>
       </c>
       <c r="C3" t="n">
-        <v>4185.37</v>
+        <v>4751.71</v>
       </c>
       <c r="D3" t="n">
-        <v>111.9</v>
+        <v>-24.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4334.5</v>
+        <v>4779.65</v>
       </c>
       <c r="C4" t="n">
-        <v>4225.35</v>
+        <v>4810.35</v>
       </c>
       <c r="D4" t="n">
-        <v>-109.15</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4223.21</v>
+        <v>4372.99</v>
       </c>
       <c r="C5" t="n">
-        <v>4298.92</v>
+        <v>4604.75</v>
       </c>
       <c r="D5" t="n">
-        <v>75.70999999999999</v>
+        <v>231.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4831.35</v>
+        <v>4600.43</v>
       </c>
       <c r="C6" t="n">
-        <v>4475.35</v>
+        <v>4510.92</v>
       </c>
       <c r="D6" t="n">
-        <v>-356</v>
+        <v>-89.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4776.09</v>
+        <v>4503.39</v>
       </c>
       <c r="C7" t="n">
-        <v>4753.24</v>
+        <v>4538.39</v>
       </c>
       <c r="D7" t="n">
-        <v>-22.85</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4779.65</v>
+        <v>4507.18</v>
       </c>
       <c r="C8" t="n">
-        <v>4809.5</v>
+        <v>4478.52</v>
       </c>
       <c r="D8" t="n">
-        <v>29.86</v>
+        <v>-28.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4372.99</v>
+        <v>4360.15</v>
       </c>
       <c r="C9" t="n">
-        <v>4604.56</v>
+        <v>4412.12</v>
       </c>
       <c r="D9" t="n">
-        <v>231.58</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4600.43</v>
+        <v>4374.15</v>
       </c>
       <c r="C10" t="n">
-        <v>4509.73</v>
+        <v>4412.22</v>
       </c>
       <c r="D10" t="n">
-        <v>-90.7</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4503.39</v>
+        <v>4390.02</v>
       </c>
       <c r="C11" t="n">
-        <v>4539.53</v>
+        <v>4423.68</v>
       </c>
       <c r="D11" t="n">
-        <v>36.14</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4507.18</v>
+        <v>4314.47</v>
       </c>
       <c r="C12" t="n">
-        <v>4478.02</v>
+        <v>4358.84</v>
       </c>
       <c r="D12" t="n">
-        <v>-29.15</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4360.15</v>
+        <v>4325.37</v>
       </c>
       <c r="C13" t="n">
-        <v>4412.82</v>
+        <v>4335.38</v>
       </c>
       <c r="D13" t="n">
-        <v>52.67</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4374.15</v>
+        <v>4450.39</v>
       </c>
       <c r="C14" t="n">
-        <v>4412.31</v>
+        <v>4400.77</v>
       </c>
       <c r="D14" t="n">
-        <v>38.15</v>
+        <v>-49.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4390.02</v>
+        <v>4298.74</v>
       </c>
       <c r="C15" t="n">
-        <v>4424.27</v>
+        <v>4404.22</v>
       </c>
       <c r="D15" t="n">
-        <v>34.25</v>
+        <v>105.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4314.47</v>
+        <v>4306.99</v>
       </c>
       <c r="C16" t="n">
-        <v>4358.77</v>
+        <v>4315.32</v>
       </c>
       <c r="D16" t="n">
-        <v>44.3</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4325.37</v>
+        <v>4274.24</v>
       </c>
       <c r="C17" t="n">
-        <v>4335.41</v>
+        <v>4302.29</v>
       </c>
       <c r="D17" t="n">
-        <v>10.04</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4450.39</v>
+        <v>4305.35</v>
       </c>
       <c r="C18" t="n">
-        <v>4401.02</v>
+        <v>4312.93</v>
       </c>
       <c r="D18" t="n">
-        <v>-49.37</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4298.74</v>
+        <v>4308.07</v>
       </c>
       <c r="C19" t="n">
-        <v>4404.72</v>
+        <v>4289.26</v>
       </c>
       <c r="D19" t="n">
-        <v>105.97</v>
+        <v>-18.81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4306.99</v>
+        <v>4309.04</v>
       </c>
       <c r="C20" t="n">
-        <v>4314.91</v>
+        <v>4295.1</v>
       </c>
       <c r="D20" t="n">
-        <v>7.92</v>
+        <v>-13.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4274.24</v>
+        <v>4349.15</v>
       </c>
       <c r="C21" t="n">
-        <v>4302.71</v>
+        <v>4327.62</v>
       </c>
       <c r="D21" t="n">
-        <v>28.47</v>
+        <v>-21.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4305.35</v>
+        <v>4461.23</v>
       </c>
       <c r="C22" t="n">
-        <v>4313.23</v>
+        <v>4392.23</v>
       </c>
       <c r="D22" t="n">
-        <v>7.88</v>
+        <v>-69.01000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4308.07</v>
+        <v>4715.25</v>
       </c>
       <c r="C23" t="n">
-        <v>4289.74</v>
+        <v>4538.53</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.34</v>
+        <v>-176.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4309.04</v>
+        <v>4668.18</v>
       </c>
       <c r="C24" t="n">
-        <v>4295.61</v>
+        <v>4652.59</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.43</v>
+        <v>-15.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4349.15</v>
+        <v>4609.6</v>
       </c>
       <c r="C25" t="n">
-        <v>4328.24</v>
+        <v>4625.33</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.91</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4461.23</v>
+        <v>4526.82</v>
       </c>
       <c r="C26" t="n">
-        <v>4392.79</v>
+        <v>4555.5</v>
       </c>
       <c r="D26" t="n">
-        <v>-68.44</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4715.25</v>
+        <v>4503.56</v>
       </c>
       <c r="C27" t="n">
-        <v>4539.38</v>
+        <v>4517.22</v>
       </c>
       <c r="D27" t="n">
-        <v>-175.87</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4668.18</v>
+        <v>4592.73</v>
       </c>
       <c r="C28" t="n">
-        <v>4653.53</v>
+        <v>4508.71</v>
       </c>
       <c r="D28" t="n">
-        <v>-14.65</v>
+        <v>-84.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4609.6</v>
+        <v>4589.92</v>
       </c>
       <c r="C29" t="n">
-        <v>4625.29</v>
+        <v>4556.06</v>
       </c>
       <c r="D29" t="n">
-        <v>15.69</v>
+        <v>-33.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4526.82</v>
+        <v>4470.92</v>
       </c>
       <c r="C30" t="n">
-        <v>4555.71</v>
+        <v>4538.09</v>
       </c>
       <c r="D30" t="n">
-        <v>28.89</v>
+        <v>67.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4503.56</v>
+        <v>4482.27</v>
       </c>
       <c r="C31" t="n">
-        <v>4517.46</v>
+        <v>4481.52</v>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4592.73</v>
+        <v>4451.33</v>
       </c>
       <c r="C32" t="n">
-        <v>4509.18</v>
+        <v>4477.84</v>
       </c>
       <c r="D32" t="n">
-        <v>-83.56</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4589.92</v>
+        <v>4202.88</v>
       </c>
       <c r="C33" t="n">
-        <v>4556.71</v>
+        <v>4310.28</v>
       </c>
       <c r="D33" t="n">
-        <v>-33.21</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4470.92</v>
+        <v>4165.5</v>
       </c>
       <c r="C34" t="n">
-        <v>4538.53</v>
+        <v>4163.11</v>
       </c>
       <c r="D34" t="n">
-        <v>67.61</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4482.27</v>
+        <v>4153.47</v>
       </c>
       <c r="C35" t="n">
-        <v>4481.83</v>
+        <v>4142.81</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.43</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4451.33</v>
+        <v>3868.33</v>
       </c>
       <c r="C36" t="n">
-        <v>4478.64</v>
+        <v>4013.57</v>
       </c>
       <c r="D36" t="n">
-        <v>27.31</v>
+        <v>145.24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4202.88</v>
+        <v>4035.89</v>
       </c>
       <c r="C37" t="n">
-        <v>4311.03</v>
+        <v>3941.97</v>
       </c>
       <c r="D37" t="n">
-        <v>108.15</v>
+        <v>-93.92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4165.5</v>
+        <v>4018.66</v>
       </c>
       <c r="C38" t="n">
-        <v>4163.58</v>
+        <v>4021.55</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.92</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4153.47</v>
+        <v>4141.48</v>
       </c>
       <c r="C39" t="n">
-        <v>4144.11</v>
+        <v>4103.68</v>
       </c>
       <c r="D39" t="n">
-        <v>-9.359999999999999</v>
+        <v>-37.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3868.33</v>
+        <v>4217.34</v>
       </c>
       <c r="C40" t="n">
-        <v>4014.59</v>
+        <v>4145.62</v>
       </c>
       <c r="D40" t="n">
-        <v>146.26</v>
+        <v>-71.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4035.89</v>
+        <v>4145.96</v>
       </c>
       <c r="C41" t="n">
-        <v>3942.48</v>
+        <v>4194.33</v>
       </c>
       <c r="D41" t="n">
-        <v>-93.40000000000001</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4018.66</v>
+        <v>4351.11</v>
       </c>
       <c r="C42" t="n">
-        <v>4023.39</v>
+        <v>4250.71</v>
       </c>
       <c r="D42" t="n">
-        <v>4.73</v>
+        <v>-100.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4141.48</v>
+        <v>4487.92</v>
       </c>
       <c r="C43" t="n">
-        <v>4104.54</v>
+        <v>4375.43</v>
       </c>
       <c r="D43" t="n">
-        <v>-36.94</v>
+        <v>-112.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4217.34</v>
+        <v>4514.87</v>
       </c>
       <c r="C44" t="n">
-        <v>4146.62</v>
+        <v>4475.06</v>
       </c>
       <c r="D44" t="n">
-        <v>-70.72</v>
+        <v>-39.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4145.96</v>
+        <v>4489.2</v>
       </c>
       <c r="C45" t="n">
-        <v>4195.06</v>
+        <v>4462.36</v>
       </c>
       <c r="D45" t="n">
-        <v>49.1</v>
+        <v>-26.83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4351.11</v>
+        <v>4515.42</v>
       </c>
       <c r="C46" t="n">
-        <v>4251.11</v>
+        <v>4477.36</v>
       </c>
       <c r="D46" t="n">
-        <v>-100</v>
+        <v>-38.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4487.92</v>
+        <v>4687.77</v>
       </c>
       <c r="C47" t="n">
-        <v>4376.22</v>
+        <v>4577.64</v>
       </c>
       <c r="D47" t="n">
-        <v>-111.71</v>
+        <v>-110.13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4514.87</v>
+        <v>4451.15</v>
       </c>
       <c r="C48" t="n">
-        <v>4475.56</v>
+        <v>4549.62</v>
       </c>
       <c r="D48" t="n">
-        <v>-39.31</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4489.2</v>
+        <v>4527.65</v>
       </c>
       <c r="C49" t="n">
-        <v>4462.58</v>
+        <v>4466.67</v>
       </c>
       <c r="D49" t="n">
-        <v>-26.62</v>
+        <v>-60.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4515.42</v>
+        <v>4369.14</v>
       </c>
       <c r="C50" t="n">
-        <v>4477.57</v>
+        <v>4434.69</v>
       </c>
       <c r="D50" t="n">
-        <v>-37.85</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4687.77</v>
+        <v>3843.01</v>
       </c>
       <c r="C51" t="n">
-        <v>4578.06</v>
+        <v>4118.84</v>
       </c>
       <c r="D51" t="n">
-        <v>-109.71</v>
+        <v>275.83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4451.15</v>
+        <v>3750.61</v>
       </c>
       <c r="C52" t="n">
-        <v>4550.15</v>
+        <v>3767.54</v>
       </c>
       <c r="D52" t="n">
-        <v>99</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4527.65</v>
+        <v>4164.43</v>
       </c>
       <c r="C53" t="n">
-        <v>4466.4</v>
+        <v>3942.58</v>
       </c>
       <c r="D53" t="n">
-        <v>-61.25</v>
+        <v>-221.85</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4369.14</v>
+        <v>4245.47</v>
       </c>
       <c r="C54" t="n">
-        <v>4435.68</v>
+        <v>4194.34</v>
       </c>
       <c r="D54" t="n">
-        <v>66.54000000000001</v>
+        <v>-51.13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3843.01</v>
+        <v>4125.41</v>
       </c>
       <c r="C55" t="n">
-        <v>4119.02</v>
+        <v>4144.72</v>
       </c>
       <c r="D55" t="n">
-        <v>276.01</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3750.61</v>
+        <v>3987.46</v>
       </c>
       <c r="C56" t="n">
-        <v>3767.49</v>
+        <v>4067.37</v>
       </c>
       <c r="D56" t="n">
-        <v>16.88</v>
+        <v>79.91</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4164.43</v>
+        <v>3894.75</v>
       </c>
       <c r="C57" t="n">
-        <v>3944.21</v>
+        <v>4030.6</v>
       </c>
       <c r="D57" t="n">
-        <v>-220.22</v>
+        <v>135.84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4245.47</v>
+        <v>3832.56</v>
       </c>
       <c r="C58" t="n">
-        <v>4196.78</v>
+        <v>3878.35</v>
       </c>
       <c r="D58" t="n">
-        <v>-48.69</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4125.41</v>
+        <v>3890.35</v>
       </c>
       <c r="C59" t="n">
-        <v>4145.49</v>
+        <v>3811.27</v>
       </c>
       <c r="D59" t="n">
-        <v>20.08</v>
+        <v>-79.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3987.46</v>
+        <v>3984.65</v>
       </c>
       <c r="C60" t="n">
-        <v>4068.08</v>
+        <v>3891.55</v>
       </c>
       <c r="D60" t="n">
-        <v>80.62</v>
+        <v>-93.09999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3894.75</v>
+        <v>3980.76</v>
       </c>
       <c r="C61" t="n">
-        <v>4031.33</v>
+        <v>3971.86</v>
       </c>
       <c r="D61" t="n">
-        <v>136.57</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3832.56</v>
+        <v>3876.76</v>
       </c>
       <c r="C62" t="n">
-        <v>3878.86</v>
+        <v>3926.27</v>
       </c>
       <c r="D62" t="n">
-        <v>46.3</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3890.35</v>
+        <v>3808.12</v>
       </c>
       <c r="C63" t="n">
-        <v>3812</v>
+        <v>3846.55</v>
       </c>
       <c r="D63" t="n">
-        <v>-78.34</v>
+        <v>38.43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3984.65</v>
+        <v>3856.03</v>
       </c>
       <c r="C64" t="n">
-        <v>3892.91</v>
+        <v>3840.65</v>
       </c>
       <c r="D64" t="n">
-        <v>-91.73999999999999</v>
+        <v>-15.37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3980.76</v>
+        <v>3934.57</v>
       </c>
       <c r="C65" t="n">
-        <v>3973.02</v>
+        <v>3880.17</v>
       </c>
       <c r="D65" t="n">
-        <v>-7.74</v>
+        <v>-54.39</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3876.76</v>
+        <v>3953.47</v>
       </c>
       <c r="C66" t="n">
-        <v>3927.01</v>
+        <v>3918.63</v>
       </c>
       <c r="D66" t="n">
-        <v>50.24</v>
+        <v>-34.84</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3808.12</v>
+        <v>4157.99</v>
       </c>
       <c r="C67" t="n">
-        <v>3847.05</v>
+        <v>4032.74</v>
       </c>
       <c r="D67" t="n">
-        <v>38.93</v>
+        <v>-125.25</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3856.03</v>
+        <v>4120.12</v>
       </c>
       <c r="C68" t="n">
-        <v>3841.24</v>
+        <v>4132.03</v>
       </c>
       <c r="D68" t="n">
-        <v>-14.79</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3934.57</v>
+        <v>3982.26</v>
       </c>
       <c r="C69" t="n">
-        <v>3880.94</v>
+        <v>4064.81</v>
       </c>
       <c r="D69" t="n">
-        <v>-53.63</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3953.47</v>
+        <v>3903.35</v>
       </c>
       <c r="C70" t="n">
-        <v>3919.36</v>
+        <v>3931.36</v>
       </c>
       <c r="D70" t="n">
-        <v>-34.11</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4157.99</v>
+        <v>3804.38</v>
       </c>
       <c r="C71" t="n">
-        <v>4033.18</v>
+        <v>3849.02</v>
       </c>
       <c r="D71" t="n">
-        <v>-124.81</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4120.12</v>
+        <v>3847.08</v>
       </c>
       <c r="C72" t="n">
-        <v>4132.89</v>
+        <v>3816.43</v>
       </c>
       <c r="D72" t="n">
-        <v>12.77</v>
+        <v>-30.66</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3982.26</v>
+        <v>3874.19</v>
       </c>
       <c r="C73" t="n">
-        <v>4064.81</v>
+        <v>3822.85</v>
       </c>
       <c r="D73" t="n">
-        <v>82.55</v>
+        <v>-51.34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3903.35</v>
+        <v>3911.06</v>
       </c>
       <c r="C74" t="n">
-        <v>3931.48</v>
+        <v>3870.62</v>
       </c>
       <c r="D74" t="n">
-        <v>28.13</v>
+        <v>-40.45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3804.38</v>
+        <v>3602.31</v>
       </c>
       <c r="C75" t="n">
-        <v>3849.54</v>
+        <v>3729.21</v>
       </c>
       <c r="D75" t="n">
-        <v>45.17</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3847.08</v>
+        <v>3292.57</v>
       </c>
       <c r="C76" t="n">
-        <v>3817.01</v>
+        <v>3418.88</v>
       </c>
       <c r="D76" t="n">
-        <v>-30.07</v>
+        <v>126.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3874.19</v>
+        <v>3425.17</v>
       </c>
       <c r="C77" t="n">
-        <v>3823.93</v>
+        <v>3366.53</v>
       </c>
       <c r="D77" t="n">
-        <v>-50.26</v>
+        <v>-58.65</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3911.06</v>
+        <v>3312.26</v>
       </c>
       <c r="C78" t="n">
-        <v>3871.74</v>
+        <v>3332.23</v>
       </c>
       <c r="D78" t="n">
-        <v>-39.33</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3602.31</v>
+        <v>3435.3</v>
       </c>
       <c r="C79" t="n">
-        <v>3730.23</v>
+        <v>3347.93</v>
       </c>
       <c r="D79" t="n">
-        <v>127.92</v>
+        <v>-87.37</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3292.57</v>
+        <v>3400.38</v>
       </c>
       <c r="C80" t="n">
-        <v>3419.16</v>
+        <v>3369.49</v>
       </c>
       <c r="D80" t="n">
-        <v>126.59</v>
+        <v>-30.88</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3425.17</v>
+        <v>3582.62</v>
       </c>
       <c r="C81" t="n">
-        <v>3367.41</v>
+        <v>3539.08</v>
       </c>
       <c r="D81" t="n">
-        <v>-57.77</v>
+        <v>-43.54</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3312.26</v>
+        <v>3568.46</v>
       </c>
       <c r="C82" t="n">
-        <v>3334.11</v>
+        <v>3592.08</v>
       </c>
       <c r="D82" t="n">
-        <v>21.85</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3435.3</v>
+        <v>3415.28</v>
       </c>
       <c r="C83" t="n">
-        <v>3348.9</v>
+        <v>3494.12</v>
       </c>
       <c r="D83" t="n">
-        <v>-86.40000000000001</v>
+        <v>78.84</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3400.38</v>
+        <v>3413.09</v>
       </c>
       <c r="C84" t="n">
-        <v>3371.21</v>
+        <v>3407.64</v>
       </c>
       <c r="D84" t="n">
-        <v>-29.17</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3582.62</v>
+        <v>3232.76</v>
       </c>
       <c r="C85" t="n">
-        <v>3540.05</v>
+        <v>3295.56</v>
       </c>
       <c r="D85" t="n">
-        <v>-42.57</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3568.46</v>
+        <v>3103.79</v>
       </c>
       <c r="C86" t="n">
-        <v>3593.03</v>
+        <v>3142</v>
       </c>
       <c r="D86" t="n">
-        <v>24.57</v>
+        <v>38.21</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3415.28</v>
+        <v>3166.63</v>
       </c>
       <c r="C87" t="n">
-        <v>3494.22</v>
+        <v>3107.16</v>
       </c>
       <c r="D87" t="n">
-        <v>78.94</v>
+        <v>-59.47</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3413.09</v>
+        <v>3092.85</v>
       </c>
       <c r="C88" t="n">
-        <v>3408.12</v>
+        <v>3104.78</v>
       </c>
       <c r="D88" t="n">
-        <v>-4.97</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3232.76</v>
+        <v>3024.54</v>
       </c>
       <c r="C89" t="n">
-        <v>3296.41</v>
+        <v>3044.31</v>
       </c>
       <c r="D89" t="n">
-        <v>63.65</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3103.79</v>
+        <v>3122.98</v>
       </c>
       <c r="C90" t="n">
-        <v>3142.54</v>
+        <v>3074.2</v>
       </c>
       <c r="D90" t="n">
-        <v>38.75</v>
+        <v>-48.78</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3166.63</v>
+        <v>3023.07</v>
       </c>
       <c r="C91" t="n">
-        <v>3107.95</v>
+        <v>3077.93</v>
       </c>
       <c r="D91" t="n">
-        <v>-58.68</v>
+        <v>54.86</v>
       </c>
     </row>
   </sheetData>

--- a/exports/eth-usd_predictions_last90.xlsx
+++ b/exports/eth-usd_predictions_last90.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,1446 +449,2669 @@
           <t>diff</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>diff_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>train_start_date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>train_end_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4831.35</v>
+        <v>4779.65</v>
       </c>
       <c r="C2" t="n">
-        <v>4475.58</v>
+        <v>4763.88</v>
       </c>
       <c r="D2" t="n">
-        <v>-355.77</v>
+        <v>-15.77</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4776.09</v>
+        <v>4372.99</v>
       </c>
       <c r="C3" t="n">
-        <v>4751.71</v>
+        <v>4840.93</v>
       </c>
       <c r="D3" t="n">
-        <v>-24.38</v>
+        <v>467.94</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4779.65</v>
+        <v>4600.43</v>
       </c>
       <c r="C4" t="n">
-        <v>4810.35</v>
+        <v>4615.38</v>
       </c>
       <c r="D4" t="n">
-        <v>30.7</v>
+        <v>14.95</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4372.99</v>
+        <v>4503.39</v>
       </c>
       <c r="C5" t="n">
-        <v>4604.75</v>
+        <v>4499.68</v>
       </c>
       <c r="D5" t="n">
-        <v>231.76</v>
+        <v>-3.71</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4600.43</v>
+        <v>4507.18</v>
       </c>
       <c r="C6" t="n">
-        <v>4510.92</v>
+        <v>4539.05</v>
       </c>
       <c r="D6" t="n">
-        <v>-89.5</v>
+        <v>31.88</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4503.39</v>
+        <v>4360.15</v>
       </c>
       <c r="C7" t="n">
-        <v>4538.39</v>
+        <v>4480.33</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>120.18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4507.18</v>
+        <v>4374.15</v>
       </c>
       <c r="C8" t="n">
-        <v>4478.52</v>
+        <v>4421.8</v>
       </c>
       <c r="D8" t="n">
-        <v>-28.66</v>
+        <v>47.65</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4360.15</v>
+        <v>4390.02</v>
       </c>
       <c r="C9" t="n">
-        <v>4412.12</v>
+        <v>4410.69</v>
       </c>
       <c r="D9" t="n">
-        <v>51.96</v>
+        <v>20.68</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4374.15</v>
+        <v>4314.47</v>
       </c>
       <c r="C10" t="n">
-        <v>4412.22</v>
+        <v>4426.27</v>
       </c>
       <c r="D10" t="n">
-        <v>38.07</v>
+        <v>111.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4390.02</v>
+        <v>4325.37</v>
       </c>
       <c r="C11" t="n">
-        <v>4423.68</v>
+        <v>4364.1</v>
       </c>
       <c r="D11" t="n">
-        <v>33.66</v>
+        <v>38.73</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4314.47</v>
+        <v>4450.39</v>
       </c>
       <c r="C12" t="n">
-        <v>4358.84</v>
+        <v>4337.16</v>
       </c>
       <c r="D12" t="n">
-        <v>44.37</v>
+        <v>-113.23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4325.37</v>
+        <v>4298.74</v>
       </c>
       <c r="C13" t="n">
-        <v>4335.38</v>
+        <v>4401.44</v>
       </c>
       <c r="D13" t="n">
-        <v>10.01</v>
+        <v>102.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4450.39</v>
+        <v>4306.99</v>
       </c>
       <c r="C14" t="n">
-        <v>4400.77</v>
+        <v>4410.04</v>
       </c>
       <c r="D14" t="n">
-        <v>-49.62</v>
+        <v>103.05</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4298.74</v>
+        <v>4274.24</v>
       </c>
       <c r="C15" t="n">
-        <v>4404.22</v>
+        <v>4317.59</v>
       </c>
       <c r="D15" t="n">
-        <v>105.47</v>
+        <v>43.35</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4306.99</v>
+        <v>4305.35</v>
       </c>
       <c r="C16" t="n">
-        <v>4315.32</v>
+        <v>4299.18</v>
       </c>
       <c r="D16" t="n">
-        <v>8.33</v>
+        <v>-6.17</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4274.24</v>
+        <v>4308.07</v>
       </c>
       <c r="C17" t="n">
-        <v>4302.29</v>
+        <v>4312.48</v>
       </c>
       <c r="D17" t="n">
-        <v>28.05</v>
+        <v>4.41</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4305.35</v>
+        <v>4309.04</v>
       </c>
       <c r="C18" t="n">
-        <v>4312.93</v>
+        <v>4297</v>
       </c>
       <c r="D18" t="n">
-        <v>7.58</v>
+        <v>-12.04</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4308.07</v>
+        <v>4349.15</v>
       </c>
       <c r="C19" t="n">
-        <v>4289.26</v>
+        <v>4297.67</v>
       </c>
       <c r="D19" t="n">
-        <v>-18.81</v>
+        <v>-51.47</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4309.04</v>
+        <v>4461.23</v>
       </c>
       <c r="C20" t="n">
-        <v>4295.1</v>
+        <v>4332.05</v>
       </c>
       <c r="D20" t="n">
-        <v>-13.94</v>
+        <v>-129.19</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4349.15</v>
+        <v>4715.25</v>
       </c>
       <c r="C21" t="n">
-        <v>4327.62</v>
+        <v>4394.69</v>
       </c>
       <c r="D21" t="n">
-        <v>-21.52</v>
+        <v>-320.56</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4461.23</v>
+        <v>4668.18</v>
       </c>
       <c r="C22" t="n">
-        <v>4392.23</v>
+        <v>4545.94</v>
       </c>
       <c r="D22" t="n">
-        <v>-69.01000000000001</v>
+        <v>-122.24</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4715.25</v>
+        <v>4609.6</v>
       </c>
       <c r="C23" t="n">
-        <v>4538.53</v>
+        <v>4663.51</v>
       </c>
       <c r="D23" t="n">
-        <v>-176.71</v>
+        <v>53.91</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4668.18</v>
+        <v>4526.82</v>
       </c>
       <c r="C24" t="n">
-        <v>4652.59</v>
+        <v>4631.71</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.59</v>
+        <v>104.89</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4609.6</v>
+        <v>4503.56</v>
       </c>
       <c r="C25" t="n">
-        <v>4625.33</v>
+        <v>4561.21</v>
       </c>
       <c r="D25" t="n">
-        <v>15.73</v>
+        <v>57.64</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4526.82</v>
+        <v>4592.73</v>
       </c>
       <c r="C26" t="n">
-        <v>4555.5</v>
+        <v>4515.97</v>
       </c>
       <c r="D26" t="n">
-        <v>28.68</v>
+        <v>-76.77</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4503.56</v>
+        <v>4589.92</v>
       </c>
       <c r="C27" t="n">
-        <v>4517.22</v>
+        <v>4511.35</v>
       </c>
       <c r="D27" t="n">
-        <v>13.66</v>
+        <v>-78.56999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4592.73</v>
+        <v>4470.92</v>
       </c>
       <c r="C28" t="n">
-        <v>4508.71</v>
+        <v>4559.09</v>
       </c>
       <c r="D28" t="n">
-        <v>-84.02</v>
+        <v>88.17</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4589.92</v>
+        <v>4482.27</v>
       </c>
       <c r="C29" t="n">
-        <v>4556.06</v>
+        <v>4545.76</v>
       </c>
       <c r="D29" t="n">
-        <v>-33.86</v>
+        <v>63.49</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4470.92</v>
+        <v>4451.33</v>
       </c>
       <c r="C30" t="n">
-        <v>4538.09</v>
+        <v>4481.67</v>
       </c>
       <c r="D30" t="n">
-        <v>67.17</v>
+        <v>30.34</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4482.27</v>
+        <v>4202.88</v>
       </c>
       <c r="C31" t="n">
-        <v>4481.52</v>
+        <v>4484.94</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.74</v>
+        <v>282.06</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4451.33</v>
+        <v>4165.5</v>
       </c>
       <c r="C32" t="n">
-        <v>4477.84</v>
+        <v>4328.95</v>
       </c>
       <c r="D32" t="n">
-        <v>26.52</v>
+        <v>163.44</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4202.88</v>
+        <v>4153.47</v>
       </c>
       <c r="C33" t="n">
-        <v>4310.28</v>
+        <v>4160.56</v>
       </c>
       <c r="D33" t="n">
-        <v>107.4</v>
+        <v>7.09</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4165.5</v>
+        <v>3868.33</v>
       </c>
       <c r="C34" t="n">
-        <v>4163.11</v>
+        <v>4142.89</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.4</v>
+        <v>274.55</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4153.47</v>
+        <v>4035.89</v>
       </c>
       <c r="C35" t="n">
-        <v>4142.81</v>
+        <v>4023.34</v>
       </c>
       <c r="D35" t="n">
-        <v>-10.66</v>
+        <v>-12.55</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3868.33</v>
+        <v>4018.66</v>
       </c>
       <c r="C36" t="n">
-        <v>4013.57</v>
+        <v>3936.45</v>
       </c>
       <c r="D36" t="n">
-        <v>145.24</v>
+        <v>-82.2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4035.89</v>
+        <v>4141.48</v>
       </c>
       <c r="C37" t="n">
-        <v>3941.97</v>
+        <v>4019.97</v>
       </c>
       <c r="D37" t="n">
-        <v>-93.92</v>
+        <v>-121.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4018.66</v>
+        <v>4217.34</v>
       </c>
       <c r="C38" t="n">
-        <v>4021.55</v>
+        <v>4108.31</v>
       </c>
       <c r="D38" t="n">
-        <v>2.89</v>
+        <v>-109.03</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4141.48</v>
+        <v>4145.96</v>
       </c>
       <c r="C39" t="n">
-        <v>4103.68</v>
+        <v>4155.3</v>
       </c>
       <c r="D39" t="n">
-        <v>-37.8</v>
+        <v>9.34</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4217.34</v>
+        <v>4351.11</v>
       </c>
       <c r="C40" t="n">
-        <v>4145.62</v>
+        <v>4201.26</v>
       </c>
       <c r="D40" t="n">
-        <v>-71.72</v>
+        <v>-149.85</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4145.96</v>
+        <v>4487.92</v>
       </c>
       <c r="C41" t="n">
-        <v>4194.33</v>
+        <v>4253.61</v>
       </c>
       <c r="D41" t="n">
-        <v>48.38</v>
+        <v>-234.32</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4351.11</v>
+        <v>4514.87</v>
       </c>
       <c r="C42" t="n">
-        <v>4250.71</v>
+        <v>4379.19</v>
       </c>
       <c r="D42" t="n">
-        <v>-100.4</v>
+        <v>-135.69</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4487.92</v>
+        <v>4489.2</v>
       </c>
       <c r="C43" t="n">
-        <v>4375.43</v>
+        <v>4484.7</v>
       </c>
       <c r="D43" t="n">
-        <v>-112.49</v>
+        <v>-4.49</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4514.87</v>
+        <v>4515.42</v>
       </c>
       <c r="C44" t="n">
-        <v>4475.06</v>
+        <v>4467.01</v>
       </c>
       <c r="D44" t="n">
-        <v>-39.81</v>
+        <v>-48.41</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4489.2</v>
+        <v>4687.77</v>
       </c>
       <c r="C45" t="n">
-        <v>4462.36</v>
+        <v>4485.37</v>
       </c>
       <c r="D45" t="n">
-        <v>-26.83</v>
+        <v>-202.4</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4515.42</v>
+        <v>4451.15</v>
       </c>
       <c r="C46" t="n">
-        <v>4477.36</v>
+        <v>4579.81</v>
       </c>
       <c r="D46" t="n">
-        <v>-38.06</v>
+        <v>128.66</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4687.77</v>
+        <v>4527.65</v>
       </c>
       <c r="C47" t="n">
-        <v>4577.64</v>
+        <v>4559.55</v>
       </c>
       <c r="D47" t="n">
-        <v>-110.13</v>
+        <v>31.9</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4451.15</v>
+        <v>4369.14</v>
       </c>
       <c r="C48" t="n">
-        <v>4549.62</v>
+        <v>4467.27</v>
       </c>
       <c r="D48" t="n">
-        <v>98.47</v>
+        <v>98.13</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4527.65</v>
+        <v>3843.01</v>
       </c>
       <c r="C49" t="n">
-        <v>4466.67</v>
+        <v>4438.27</v>
       </c>
       <c r="D49" t="n">
-        <v>-60.98</v>
+        <v>595.26</v>
+      </c>
+      <c r="E49" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4369.14</v>
+        <v>3750.61</v>
       </c>
       <c r="C50" t="n">
-        <v>4434.69</v>
+        <v>4129.1</v>
       </c>
       <c r="D50" t="n">
-        <v>65.55</v>
+        <v>378.49</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3843.01</v>
+        <v>4164.43</v>
       </c>
       <c r="C51" t="n">
-        <v>4118.84</v>
+        <v>3752.33</v>
       </c>
       <c r="D51" t="n">
-        <v>275.83</v>
+        <v>-412.1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3750.61</v>
+        <v>4245.47</v>
       </c>
       <c r="C52" t="n">
-        <v>3767.54</v>
+        <v>3932.19</v>
       </c>
       <c r="D52" t="n">
-        <v>16.93</v>
+        <v>-313.27</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4164.43</v>
+        <v>4125.41</v>
       </c>
       <c r="C53" t="n">
-        <v>3942.58</v>
+        <v>4202.86</v>
       </c>
       <c r="D53" t="n">
-        <v>-221.85</v>
+        <v>77.45</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4245.47</v>
+        <v>3987.46</v>
       </c>
       <c r="C54" t="n">
-        <v>4194.34</v>
+        <v>4161.12</v>
       </c>
       <c r="D54" t="n">
-        <v>-51.13</v>
+        <v>173.66</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4125.41</v>
+        <v>3894.75</v>
       </c>
       <c r="C55" t="n">
-        <v>4144.72</v>
+        <v>4076.35</v>
       </c>
       <c r="D55" t="n">
-        <v>19.31</v>
+        <v>181.6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3987.46</v>
+        <v>3832.56</v>
       </c>
       <c r="C56" t="n">
-        <v>4067.37</v>
+        <v>4033.77</v>
       </c>
       <c r="D56" t="n">
-        <v>79.91</v>
+        <v>201.21</v>
+      </c>
+      <c r="E56" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3894.75</v>
+        <v>3890.35</v>
       </c>
       <c r="C57" t="n">
-        <v>4030.6</v>
+        <v>3880.5</v>
       </c>
       <c r="D57" t="n">
-        <v>135.84</v>
+        <v>-9.84</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3832.56</v>
+        <v>3984.65</v>
       </c>
       <c r="C58" t="n">
-        <v>3878.35</v>
+        <v>3810.13</v>
       </c>
       <c r="D58" t="n">
-        <v>45.8</v>
+        <v>-174.52</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3890.35</v>
+        <v>3980.76</v>
       </c>
       <c r="C59" t="n">
-        <v>3811.27</v>
+        <v>3894.83</v>
       </c>
       <c r="D59" t="n">
-        <v>-79.08</v>
+        <v>-85.93000000000001</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3984.65</v>
+        <v>3876.76</v>
       </c>
       <c r="C60" t="n">
-        <v>3891.55</v>
+        <v>3977.17</v>
       </c>
       <c r="D60" t="n">
-        <v>-93.09999999999999</v>
+        <v>100.41</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3980.76</v>
+        <v>3808.12</v>
       </c>
       <c r="C61" t="n">
-        <v>3971.86</v>
+        <v>3931.44</v>
       </c>
       <c r="D61" t="n">
-        <v>-8.9</v>
+        <v>123.32</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3876.76</v>
+        <v>3856.03</v>
       </c>
       <c r="C62" t="n">
-        <v>3926.27</v>
+        <v>3848.27</v>
       </c>
       <c r="D62" t="n">
-        <v>49.51</v>
+        <v>-7.75</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3808.12</v>
+        <v>3934.57</v>
       </c>
       <c r="C63" t="n">
-        <v>3846.55</v>
+        <v>3841.44</v>
       </c>
       <c r="D63" t="n">
-        <v>38.43</v>
+        <v>-93.13</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3856.03</v>
+        <v>3953.47</v>
       </c>
       <c r="C64" t="n">
-        <v>3840.65</v>
+        <v>3881.88</v>
       </c>
       <c r="D64" t="n">
-        <v>-15.37</v>
+        <v>-71.59</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3934.57</v>
+        <v>4157.99</v>
       </c>
       <c r="C65" t="n">
-        <v>3880.17</v>
+        <v>3917.91</v>
       </c>
       <c r="D65" t="n">
-        <v>-54.39</v>
+        <v>-240.08</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3953.47</v>
+        <v>4120.12</v>
       </c>
       <c r="C66" t="n">
-        <v>3918.63</v>
+        <v>4038.22</v>
       </c>
       <c r="D66" t="n">
-        <v>-34.84</v>
+        <v>-81.90000000000001</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4157.99</v>
+        <v>3982.26</v>
       </c>
       <c r="C67" t="n">
-        <v>4032.74</v>
+        <v>4137</v>
       </c>
       <c r="D67" t="n">
-        <v>-125.25</v>
+        <v>154.74</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4120.12</v>
+        <v>3903.35</v>
       </c>
       <c r="C68" t="n">
-        <v>4132.03</v>
+        <v>4068.58</v>
       </c>
       <c r="D68" t="n">
-        <v>11.91</v>
+        <v>165.23</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3982.26</v>
+        <v>3804.38</v>
       </c>
       <c r="C69" t="n">
-        <v>4064.81</v>
+        <v>3934.32</v>
       </c>
       <c r="D69" t="n">
-        <v>82.54000000000001</v>
+        <v>129.95</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3903.35</v>
+        <v>3847.08</v>
       </c>
       <c r="C70" t="n">
-        <v>3931.36</v>
+        <v>3851.19</v>
       </c>
       <c r="D70" t="n">
-        <v>28.01</v>
+        <v>4.11</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3804.38</v>
+        <v>3874.19</v>
       </c>
       <c r="C71" t="n">
-        <v>3849.02</v>
+        <v>3818.56</v>
       </c>
       <c r="D71" t="n">
-        <v>44.64</v>
+        <v>-55.62</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3847.08</v>
+        <v>3911.06</v>
       </c>
       <c r="C72" t="n">
-        <v>3816.43</v>
+        <v>3824.7</v>
       </c>
       <c r="D72" t="n">
-        <v>-30.66</v>
+        <v>-86.37</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3874.19</v>
+        <v>3602.31</v>
       </c>
       <c r="C73" t="n">
-        <v>3822.85</v>
+        <v>3875.07</v>
       </c>
       <c r="D73" t="n">
-        <v>-51.34</v>
+        <v>272.76</v>
+      </c>
+      <c r="E73" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3911.06</v>
+        <v>3292.57</v>
       </c>
       <c r="C74" t="n">
-        <v>3870.62</v>
+        <v>3736.95</v>
       </c>
       <c r="D74" t="n">
-        <v>-40.45</v>
+        <v>444.38</v>
+      </c>
+      <c r="E74" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3602.31</v>
+        <v>3425.17</v>
       </c>
       <c r="C75" t="n">
-        <v>3729.21</v>
+        <v>3420.34</v>
       </c>
       <c r="D75" t="n">
-        <v>126.9</v>
+        <v>-4.83</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3292.57</v>
+        <v>3312.26</v>
       </c>
       <c r="C76" t="n">
-        <v>3418.88</v>
+        <v>3368.63</v>
       </c>
       <c r="D76" t="n">
-        <v>126.3</v>
+        <v>56.37</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3425.17</v>
+        <v>3435.3</v>
       </c>
       <c r="C77" t="n">
-        <v>3366.53</v>
+        <v>3332.76</v>
       </c>
       <c r="D77" t="n">
-        <v>-58.65</v>
+        <v>-102.54</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3312.26</v>
+        <v>3400.38</v>
       </c>
       <c r="C78" t="n">
-        <v>3332.23</v>
+        <v>3347.79</v>
       </c>
       <c r="D78" t="n">
-        <v>19.98</v>
+        <v>-52.59</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3435.3</v>
+        <v>3582.62</v>
       </c>
       <c r="C79" t="n">
-        <v>3347.93</v>
+        <v>3370.12</v>
       </c>
       <c r="D79" t="n">
-        <v>-87.37</v>
+        <v>-212.51</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-5.93</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3400.38</v>
+        <v>3568.46</v>
       </c>
       <c r="C80" t="n">
-        <v>3369.49</v>
+        <v>3539.78</v>
       </c>
       <c r="D80" t="n">
-        <v>-30.88</v>
+        <v>-28.68</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3582.62</v>
+        <v>3415.28</v>
       </c>
       <c r="C81" t="n">
-        <v>3539.08</v>
+        <v>3594.81</v>
       </c>
       <c r="D81" t="n">
-        <v>-43.54</v>
+        <v>179.53</v>
+      </c>
+      <c r="E81" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3568.46</v>
+        <v>3413.09</v>
       </c>
       <c r="C82" t="n">
-        <v>3592.08</v>
+        <v>3496.24</v>
       </c>
       <c r="D82" t="n">
-        <v>23.62</v>
+        <v>83.15000000000001</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3415.28</v>
+        <v>3232.76</v>
       </c>
       <c r="C83" t="n">
-        <v>3494.12</v>
+        <v>3409.94</v>
       </c>
       <c r="D83" t="n">
-        <v>78.84</v>
+        <v>177.18</v>
+      </c>
+      <c r="E83" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3413.09</v>
+        <v>3103.79</v>
       </c>
       <c r="C84" t="n">
-        <v>3407.64</v>
+        <v>3297.77</v>
       </c>
       <c r="D84" t="n">
-        <v>-5.46</v>
+        <v>193.99</v>
+      </c>
+      <c r="E84" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3232.76</v>
+        <v>3166.63</v>
       </c>
       <c r="C85" t="n">
-        <v>3295.56</v>
+        <v>3142.32</v>
       </c>
       <c r="D85" t="n">
-        <v>62.8</v>
+        <v>-24.31</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3103.79</v>
+        <v>3092.85</v>
       </c>
       <c r="C86" t="n">
-        <v>3142</v>
+        <v>3107.97</v>
       </c>
       <c r="D86" t="n">
-        <v>38.21</v>
+        <v>15.13</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3166.63</v>
+        <v>3024.54</v>
       </c>
       <c r="C87" t="n">
-        <v>3107.16</v>
+        <v>3106.06</v>
       </c>
       <c r="D87" t="n">
-        <v>-59.47</v>
+        <v>81.52</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3092.85</v>
+        <v>3122.98</v>
       </c>
       <c r="C88" t="n">
-        <v>3104.78</v>
+        <v>3044.86</v>
       </c>
       <c r="D88" t="n">
-        <v>11.94</v>
+        <v>-78.12</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3024.54</v>
+        <v>3023.07</v>
       </c>
       <c r="C89" t="n">
-        <v>3044.31</v>
+        <v>3075.23</v>
       </c>
       <c r="D89" t="n">
-        <v>19.78</v>
+        <v>52.16</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3122.98</v>
+        <v>2831.78</v>
       </c>
       <c r="C90" t="n">
-        <v>3074.2</v>
+        <v>3078.99</v>
       </c>
       <c r="D90" t="n">
-        <v>-48.78</v>
+        <v>247.21</v>
+      </c>
+      <c r="E90" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3023.07</v>
+        <v>2765.7</v>
       </c>
       <c r="C91" t="n">
-        <v>3077.93</v>
+        <v>2899.81</v>
       </c>
       <c r="D91" t="n">
-        <v>54.86</v>
-      </c>
+        <v>134.11</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AVG_TRIM</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>(ex max/min)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
